--- a/extenbooks/S303_extenbook.xlsx
+++ b/extenbooks/S303_extenbook.xlsx
@@ -4468,7 +4468,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -5411,11 +5411,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5438,88 +5438,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Engel Curve of Necessaries, Case I</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S303_research.json", "adequacy_report": "Technical/docs/chapters/CH3_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S303_DPR.md", "epr": "Technical/docs/series/S303_EPR.md", "loader": "Technical/code/L01_loaders/L01_S303_load.py", "processor": "Technical/code/P02_processors/P02_S303_construct.py", "validator": "Technical/code/V03_validators/V03_S303_validate.py", "processed": "Technical/data/processed/S303.parquet", "chopped_csv": "Technical/chopped/S303.csv", "extenbook_xlsx": "Technical/extenbooks/S303_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S303-A"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_2016_EQ_3_4_3_11"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S303_extenbook.xlsx
+++ b/extenbooks/S303_extenbook.xlsx
@@ -4415,7 +4415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A113"/>
+  <dimension ref="A1:A118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4454,7 +4454,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-wave-a-ch3 (Phase 5-8 fanout)</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S303_research.json`</t>
+          <t>- Series research notes: `Technical/research/S303_research.json`</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>## From the Book</t>
         </is>
       </c>
     </row>
@@ -4594,62 +4594,58 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>&gt; people buy proportionately less of necessary goods, and hence proportionately more of other (luxury) goods, as their income increases [...] This is known as Engel's Law of consumer demand.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>&gt; -- Shaikh (2016), Chapter 3, p. 92 &lt;!-- kb: ch03, p.92 (ch03_micro_foundations.md, Engel's Law) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>| **S303-A** | n/a (theoretical) | Shaikh 2016 eq (3.5), p. 91; Figure 3.5 axis bounds p. 94 | model units of expenditure | analytic regeneration from equation |</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>## 3. Sources</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1. Income grid y in [0, 60], 121 points.</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2. Calibration: x1min(y) = y^0.5, c = 0.5, p1 = 1 (Case I, shared with S301/S302).</t>
+          <t>| **S303-A** (the dataset's single data column) | n/a (theoretical) | Shaikh 2016 eq (3.5), p. 91; Figure 3.5 axis bounds p. 94 | model units of expenditure | analytic regeneration from equation |</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>3. Evaluate p1*x1 = (1 - c)*x1min(y) + c*y = 0.5*y^0.5 + 0.5*y.</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4. At y=0 the curve is at 0; at y=60 the curve is 0.5*sqrt(60) + 30 ~ 33.87 (within the printed [0,40] axis).</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -4659,186 +4655,186 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>**Formula**: `p1*x1 = (1 - c) * p1*x1min(y) + c*y`</t>
+          <t>1. Income grid y in [0, 60], 121 points.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2. Calibration: x1min(y) = y^0.5, c = 0.5, p1 = 1 (Case I, shared with S301/S302).</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>3. Evaluate p1*x1 = (1 - c)*x1min(y) + c*y = 0.5*y^0.5 + 0.5*y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4. At y=0 the curve is at 0; at y=60 the curve is 0.5*sqrt(60) + 30 ~ 33.87 (within the printed [0,40] axis).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>**Formula**: `p1*x1 = (1 - c) * p1*x1min(y) + c*y`</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>- **No year dimension**. y in [0, 60].</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>## 6. Units</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>- **Output**: expenditure on necessaries (model units).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-    </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>1. Same calibration as S301/S302. The integrated curve passes through the origin.</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2. Curvature is mild because c=0.5 dominates at high y; the linear-in-y term (c*y = 0.5*y) is the main contributor to the curve at y &gt; 4.</t>
+          <t>- **Output**: expenditure on necessaries (model units).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>3. No empirical content; no proxy; no synthetic fill.</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1. Same calibration as S301/S302. The integrated curve passes through the origin.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: none</t>
+          <t>2. Curvature is mild because c=0.5 dominates at high y; the linear-in-y term (c*y = 0.5*y) is the main contributor to the curve at y &gt; 4.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.5 on p. 94</t>
+          <t>3. No empirical content; no proxy; no synthetic fill.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.5</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>- **Predecessor series**: none (first constructed in this dataset).</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>- **Tolerance**: PASS_THEORETICAL mode. Checks: monotone rising (saturating shape is concave), all values within [0.0, 40.0].</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.5 on p. 94</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>- **Source-book text**: Shaikh (2016) Chapter 3, extracted in the project knowledge base (ch03_micro_foundations.md).</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4">
+      <c r="A69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: the validator's theoretical-curve mode (checks the curve's shape and bounds rather than matching tabulated values). Checks: monotone rising (saturating shape is concave), all values within [0.0, 40.0].</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4">
         <f>== EPR: S303_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t># S303 -- Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>**Series**: S303 -- Engel Curve of Necessaries, Case I</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>**Content type**: `theoretical`</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>**Related**: `S303_DPR.md`, `Technical/research/S303_research.json`</t>
+          <t># S303 -- Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4848,27 +4844,35 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Series**: S303 -- Engel Curve of Necessaries, Case I</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>**Record type**: Extension Provenance Record</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>## 1. Classification</t>
+          <t>**Content type**: `theoretical`</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>`theoretical`; integrated Engel curve from eq (3.5).</t>
+          <t>**Related**: `S303_DPR.md`, `Technical/research/S303_research.json`</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4882,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4892,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>**Extension method**: `none`. Re-evaluated from eq (3.5) each run.</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4902,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>## 3. Worked example</t>
+          <t>`theoretical`; integrated Engel curve from eq (3.5).</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4912,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Pass-through; the curve at y=0 is 0, at y=60 is ~33.87. Concave, monotone rising.</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4922,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>**Extension method**: `none`. Re-evaluated from eq (3.5) each time the data-loading step runs.</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4932,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>No proxy substitution. See `S303_DPR.md` for source details.</t>
+          <t>## 3. Worked example</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4942,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>Pass-through; the curve at y=0 is 0, at y=60 is ~33.87. Concave, monotone rising.</t>
         </is>
       </c>
     </row>
@@ -4948,86 +4952,109 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>No synthetic gap-filling in the prohibited sense. The DPR documents any</t>
+          <t>## 4. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>analytic regeneration or library-data dependence explicitly.</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>No proxy substitution. See `S303_DPR.md` for source details.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>No synthetic gap-filling in the prohibited sense. The companion Data Provenance Record (DPR) documents any analytic regeneration or library-data dependence explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>Calibration drift, bound violation, shape failure (would indicate parameter change).</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>No CD2 predecessor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-    </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>## 8. Why no API extension applies</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>## 7. Predecessor divergence pre-disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>Predecessor series: none (first constructed in this dataset).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>## 8. Why no API extension applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>Anu-framework rule on extension only applies to `time_series` series. The</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>chopped CSV is the final published deliverable.</t>
         </is>
@@ -5221,7 +5248,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5384,7 +5411,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-18T22:01:48.224591+00:00</t>
+          <t>2026-07-02T06:22:08.955818+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S303_extenbook.xlsx
+++ b/extenbooks/S303_extenbook.xlsx
@@ -4468,7 +4468,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: theoretical_validated</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-02T06:22:08.955818+00:00</t>
+          <t>2026-07-11T03:44:24.659834+00:00</t>
         </is>
       </c>
     </row>
@@ -5438,11 +5438,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5465,6 +5465,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_EQ_3_4_3_11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>theoretical_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable analytic Engel curve (Shaikh Fig 3.5): integrated expenditure on necessaries vs income under Case I, 121 clean points. Renders as an x-y curve over the income grid ('year' index column, NOT calendar years). TRIAGE_PRESCREEN EMPTY flag did not apply but the index-as-year pattern does; L01/P02 exist and replicate.py builds it (PASS). Caveat: agent-chosen Case I calibration (DPR \u00a77) governs levels; shape is the faithful object. KB coverage: ch03 IS extracted in the book KB (HDARP v3.3 Sraffa OCR campaign) (Body_Text/ch03_micro_foundations.md + Figures/ch03/ch03_fig_3.5.md); the chapter-3 figure quotes in the research JSON ARE verifiable against KB, and a 'From the book' section can be populated in the explainer (doc-side backfill).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S303_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S303_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Theoretical curve; no historical observations. Calibrated to match the printed axis bounds of the figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>expenditure on necessaries (model units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
